--- a/data/기온.xlsx
+++ b/data/기온.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2025\0. 스터디\2025\streamlit_study\사업계획_공급량예측_상품별\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_공급량예측_상품별\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{84F1E06C-3D6E-4D53-A4DB-5FE5A21094DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C916368-43A9-42C3-AA29-42B6823AC9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45C73865-3F39-4EA8-9E93-177781A84992}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,6 +212,12 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -395,7 +401,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -507,6 +513,21 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,12 +660,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1021,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95154CA9-0CA3-48E3-B438-E6B08D231B8B}">
-  <dimension ref="A1:C5730"/>
+  <dimension ref="A1:C6217"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -63655,7 +63679,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="5699" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5699" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5699" s="1">
         <v>45869</v>
       </c>
@@ -63666,345 +63690,3416 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="5700" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5700" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5700" s="1">
         <v>45870</v>
       </c>
       <c r="B5700">
         <v>143</v>
       </c>
-      <c r="C5700">
+      <c r="C5700" s="2">
         <v>30.4</v>
       </c>
     </row>
-    <row r="5701" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5701" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5701" s="1">
         <v>45871</v>
       </c>
       <c r="B5701">
         <v>143</v>
       </c>
-      <c r="C5701">
+      <c r="C5701" s="2">
         <v>30.9</v>
       </c>
     </row>
-    <row r="5702" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5702" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5702" s="1">
         <v>45872</v>
       </c>
       <c r="B5702">
         <v>143</v>
       </c>
-      <c r="C5702">
+      <c r="C5702" s="2">
         <v>28.9</v>
       </c>
     </row>
-    <row r="5703" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5703" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5703" s="1">
         <v>45873</v>
       </c>
       <c r="B5703">
         <v>143</v>
       </c>
-      <c r="C5703">
+      <c r="C5703" s="2">
         <v>28.2</v>
       </c>
     </row>
-    <row r="5704" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5704" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5704" s="1">
         <v>45874</v>
       </c>
       <c r="B5704">
         <v>143</v>
       </c>
-      <c r="C5704">
+      <c r="C5704" s="2">
         <v>29.7</v>
       </c>
     </row>
-    <row r="5705" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5705" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5705" s="1">
         <v>45875</v>
       </c>
       <c r="B5705">
         <v>143</v>
       </c>
-      <c r="C5705">
+      <c r="C5705" s="2">
         <v>28.5</v>
       </c>
     </row>
-    <row r="5706" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5706" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5706" s="1">
         <v>45876</v>
       </c>
       <c r="B5706">
         <v>143</v>
       </c>
-      <c r="C5706">
+      <c r="C5706" s="2">
         <v>27.4</v>
       </c>
     </row>
-    <row r="5707" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5707" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5707" s="1">
         <v>45877</v>
       </c>
       <c r="B5707">
         <v>143</v>
       </c>
-      <c r="C5707">
+      <c r="C5707" s="2">
         <v>26.9</v>
       </c>
     </row>
-    <row r="5708" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5708" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5708" s="1">
         <v>45878</v>
       </c>
       <c r="B5708">
         <v>143</v>
       </c>
-      <c r="C5708">
+      <c r="C5708" s="2">
         <v>24.5</v>
       </c>
     </row>
-    <row r="5709" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5709" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5709" s="1">
         <v>45879</v>
       </c>
       <c r="B5709">
         <v>143</v>
       </c>
-      <c r="C5709">
+      <c r="C5709" s="2">
         <v>25.2</v>
       </c>
     </row>
-    <row r="5710" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5710" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5710" s="1">
         <v>45880</v>
       </c>
       <c r="B5710">
         <v>143</v>
       </c>
-      <c r="C5710">
+      <c r="C5710" s="2">
         <v>24.4</v>
       </c>
     </row>
-    <row r="5711" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5711" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5711" s="1">
         <v>45881</v>
       </c>
       <c r="B5711">
         <v>143</v>
       </c>
-      <c r="C5711">
+      <c r="C5711" s="2">
         <v>22.8</v>
       </c>
     </row>
-    <row r="5712" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5712" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5712" s="1">
         <v>45882</v>
       </c>
       <c r="B5712">
         <v>143</v>
       </c>
-      <c r="C5712">
+      <c r="C5712" s="2">
         <v>27.5</v>
       </c>
     </row>
-    <row r="5713" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5713" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5713" s="1">
         <v>45883</v>
       </c>
       <c r="B5713">
         <v>143</v>
       </c>
-      <c r="C5713">
+      <c r="C5713" s="2">
         <v>29.8</v>
       </c>
     </row>
-    <row r="5714" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5714" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5714" s="1">
         <v>45884</v>
       </c>
       <c r="B5714">
         <v>143</v>
       </c>
-      <c r="C5714">
+      <c r="C5714" s="2">
         <v>29.5</v>
       </c>
     </row>
-    <row r="5715" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5715" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5715" s="1">
         <v>45885</v>
       </c>
       <c r="B5715">
         <v>143</v>
       </c>
-      <c r="C5715">
+      <c r="C5715" s="2">
         <v>29.7</v>
       </c>
     </row>
-    <row r="5716" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5716" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5716" s="1">
         <v>45886</v>
       </c>
       <c r="B5716">
         <v>143</v>
       </c>
-      <c r="C5716">
+      <c r="C5716" s="2">
         <v>28.8</v>
       </c>
     </row>
-    <row r="5717" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5717" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5717" s="1">
         <v>45887</v>
       </c>
       <c r="B5717">
         <v>143</v>
       </c>
-      <c r="C5717">
+      <c r="C5717" s="2">
         <v>29.5</v>
       </c>
     </row>
-    <row r="5718" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5718" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5718" s="1">
         <v>45888</v>
       </c>
       <c r="B5718">
         <v>143</v>
       </c>
-      <c r="C5718">
+      <c r="C5718" s="2">
         <v>30.8</v>
       </c>
     </row>
-    <row r="5719" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5719" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5719" s="1">
         <v>45889</v>
       </c>
       <c r="B5719">
         <v>143</v>
       </c>
-      <c r="C5719">
+      <c r="C5719" s="2">
         <v>30.4</v>
       </c>
     </row>
-    <row r="5720" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5720" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5720" s="1">
         <v>45890</v>
       </c>
       <c r="B5720">
         <v>143</v>
       </c>
-      <c r="C5720">
+      <c r="C5720" s="2">
         <v>30.1</v>
       </c>
     </row>
-    <row r="5721" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5721" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5721" s="1">
         <v>45891</v>
       </c>
       <c r="B5721">
         <v>143</v>
       </c>
-      <c r="C5721">
+      <c r="C5721" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="5722" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5722" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5722" s="1">
         <v>45892</v>
       </c>
       <c r="B5722">
         <v>143</v>
       </c>
-      <c r="C5722">
+      <c r="C5722" s="2">
         <v>30.8</v>
       </c>
     </row>
-    <row r="5723" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5723" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5723" s="1">
         <v>45893</v>
       </c>
       <c r="B5723">
         <v>143</v>
       </c>
-      <c r="C5723">
+      <c r="C5723" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="5724" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5724" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5724" s="1">
         <v>45894</v>
       </c>
       <c r="B5724">
         <v>143</v>
       </c>
-      <c r="C5724">
+      <c r="C5724" s="2">
         <v>30.8</v>
       </c>
     </row>
-    <row r="5725" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5725" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5725" s="1">
         <v>45895</v>
       </c>
       <c r="B5725">
         <v>143</v>
       </c>
-      <c r="C5725">
+      <c r="C5725" s="2">
         <v>28.9</v>
       </c>
     </row>
-    <row r="5726" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5726" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5726" s="1">
         <v>45896</v>
       </c>
       <c r="B5726">
         <v>143</v>
       </c>
-      <c r="C5726">
+      <c r="C5726" s="2">
         <v>28.3</v>
       </c>
     </row>
-    <row r="5727" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5727" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5727" s="1">
         <v>45897</v>
       </c>
       <c r="B5727">
         <v>143</v>
       </c>
-      <c r="C5727">
+      <c r="C5727" s="2">
         <v>28.3</v>
       </c>
     </row>
-    <row r="5728" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5728" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5728" s="1">
         <v>45898</v>
       </c>
       <c r="B5728">
         <v>143</v>
       </c>
-      <c r="C5728">
+      <c r="C5728" s="2">
         <v>30.6</v>
       </c>
     </row>
-    <row r="5729" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5729" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5729" s="1">
         <v>45899</v>
       </c>
       <c r="B5729">
         <v>143</v>
       </c>
-      <c r="C5729">
+      <c r="C5729" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="5730" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5730" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5730" s="1">
         <v>45900</v>
       </c>
       <c r="B5730">
         <v>143</v>
       </c>
-      <c r="C5730">
+      <c r="C5730" s="2">
         <v>27.8</v>
+      </c>
+    </row>
+    <row r="5731" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5731" s="1">
+        <v>45901</v>
+      </c>
+      <c r="C5731" s="2">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="5732" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5732" s="1">
+        <v>45902</v>
+      </c>
+      <c r="C5732" s="2">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="5733" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5733" s="1">
+        <v>45903</v>
+      </c>
+      <c r="C5733" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5734" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5734" s="1">
+        <v>45904</v>
+      </c>
+      <c r="C5734" s="2">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5735" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5735" s="1">
+        <v>45905</v>
+      </c>
+      <c r="C5735" s="2">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="5736" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5736" s="1">
+        <v>45906</v>
+      </c>
+      <c r="C5736" s="2">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="5737" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5737" s="1">
+        <v>45907</v>
+      </c>
+      <c r="C5737" s="2">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="5738" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5738" s="1">
+        <v>45908</v>
+      </c>
+      <c r="C5738" s="2">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="5739" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5739" s="1">
+        <v>45909</v>
+      </c>
+      <c r="C5739" s="2">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="5740" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5740" s="1">
+        <v>45910</v>
+      </c>
+      <c r="C5740" s="2">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="5741" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5741" s="1">
+        <v>45911</v>
+      </c>
+      <c r="C5741" s="2">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="5742" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5742" s="1">
+        <v>45912</v>
+      </c>
+      <c r="C5742" s="2">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="5743" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5743" s="1">
+        <v>45913</v>
+      </c>
+      <c r="C5743" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5744" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5744" s="1">
+        <v>45914</v>
+      </c>
+      <c r="C5744" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5745" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5745" s="1">
+        <v>45915</v>
+      </c>
+      <c r="C5745" s="2">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="5746" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5746" s="1">
+        <v>45916</v>
+      </c>
+      <c r="C5746" s="2">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="5747" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5747" s="1">
+        <v>45917</v>
+      </c>
+      <c r="C5747" s="2">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5748" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5748" s="1">
+        <v>45918</v>
+      </c>
+      <c r="C5748" s="2">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="5749" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5749" s="1">
+        <v>45919</v>
+      </c>
+      <c r="C5749" s="2">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="5750" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5750" s="1">
+        <v>45920</v>
+      </c>
+      <c r="C5750" s="2">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="5751" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5751" s="1">
+        <v>45921</v>
+      </c>
+      <c r="C5751" s="2">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="5752" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5752" s="1">
+        <v>45922</v>
+      </c>
+      <c r="C5752" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5753" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5753" s="1">
+        <v>45923</v>
+      </c>
+      <c r="C5753" s="2">
+        <v>21.2</v>
+      </c>
+    </row>
+    <row r="5754" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5754" s="1">
+        <v>45924</v>
+      </c>
+      <c r="C5754" s="2">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="5755" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5755" s="1">
+        <v>45925</v>
+      </c>
+      <c r="C5755" s="2">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="5756" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5756" s="1">
+        <v>45926</v>
+      </c>
+      <c r="C5756" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5757" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5757" s="1">
+        <v>45927</v>
+      </c>
+      <c r="C5757" s="2">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="5758" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5758" s="1">
+        <v>45928</v>
+      </c>
+      <c r="C5758" s="2">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="5759" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5759" s="1">
+        <v>45929</v>
+      </c>
+      <c r="C5759" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5760" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5760" s="1">
+        <v>45930</v>
+      </c>
+      <c r="C5760" s="2">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="5761" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5761" s="1">
+        <v>45931</v>
+      </c>
+      <c r="C5761" s="2">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="5762" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5762" s="1">
+        <v>45932</v>
+      </c>
+      <c r="C5762" s="2">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="5763" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5763" s="1">
+        <v>45933</v>
+      </c>
+      <c r="C5763" s="2">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="5764" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5764" s="1">
+        <v>45934</v>
+      </c>
+      <c r="C5764" s="2">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="5765" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5765" s="1">
+        <v>45935</v>
+      </c>
+      <c r="C5765" s="2">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="5766" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5766" s="1">
+        <v>45936</v>
+      </c>
+      <c r="C5766" s="2">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="5767" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5767" s="1">
+        <v>45937</v>
+      </c>
+      <c r="C5767" s="2">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="5768" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5768" s="1">
+        <v>45938</v>
+      </c>
+      <c r="C5768" s="2">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="5769" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5769" s="1">
+        <v>45939</v>
+      </c>
+      <c r="C5769" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5770" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5770" s="1">
+        <v>45940</v>
+      </c>
+      <c r="C5770" s="2">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="5771" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5771" s="1">
+        <v>45941</v>
+      </c>
+      <c r="C5771" s="2">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="5772" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5772" s="1">
+        <v>45942</v>
+      </c>
+      <c r="C5772" s="2">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="5773" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5773" s="1">
+        <v>45943</v>
+      </c>
+      <c r="C5773" s="2">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="5774" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5774" s="1">
+        <v>45944</v>
+      </c>
+      <c r="C5774" s="2">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="5775" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5775" s="1">
+        <v>45945</v>
+      </c>
+      <c r="C5775" s="2">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="5776" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5776" s="1">
+        <v>45946</v>
+      </c>
+      <c r="C5776" s="2">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="5777" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5777" s="1">
+        <v>45947</v>
+      </c>
+      <c r="C5777" s="2">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="5778" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5778" s="1">
+        <v>45948</v>
+      </c>
+      <c r="C5778" s="2">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="5779" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5779" s="1">
+        <v>45949</v>
+      </c>
+      <c r="C5779" s="2">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="5780" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5780" s="1">
+        <v>45950</v>
+      </c>
+      <c r="C5780" s="2">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="5781" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5781" s="1">
+        <v>45951</v>
+      </c>
+      <c r="C5781" s="2">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="5782" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5782" s="1">
+        <v>45952</v>
+      </c>
+      <c r="C5782" s="2">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="5783" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5783" s="1">
+        <v>45953</v>
+      </c>
+      <c r="C5783" s="2">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="5784" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5784" s="1">
+        <v>45954</v>
+      </c>
+      <c r="C5784" s="2">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="5785" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5785" s="1">
+        <v>45955</v>
+      </c>
+      <c r="C5785" s="2">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="5786" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5786" s="1">
+        <v>45956</v>
+      </c>
+      <c r="C5786" s="2">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="5787" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5787" s="1">
+        <v>45957</v>
+      </c>
+      <c r="C5787" s="2">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="5788" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5788" s="1">
+        <v>45958</v>
+      </c>
+      <c r="C5788" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="5789" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5789" s="1">
+        <v>45959</v>
+      </c>
+      <c r="C5789" s="2">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="5790" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5790" s="1">
+        <v>45960</v>
+      </c>
+      <c r="C5790" s="2">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="5791" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5791" s="1">
+        <v>45961</v>
+      </c>
+      <c r="C5791" s="2">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="5792" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5792" s="1">
+        <v>45962</v>
+      </c>
+      <c r="C5792" s="2">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="5793" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5793" s="1">
+        <v>45963</v>
+      </c>
+      <c r="C5793" s="2">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="5794" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5794" s="1">
+        <v>45964</v>
+      </c>
+      <c r="C5794" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="5795" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5795" s="1">
+        <v>45965</v>
+      </c>
+      <c r="C5795" s="2">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="5796" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5796" s="1">
+        <v>45966</v>
+      </c>
+      <c r="C5796" s="2">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="5797" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5797" s="1">
+        <v>45967</v>
+      </c>
+      <c r="C5797" s="2">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="5798" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5798" s="1">
+        <v>45968</v>
+      </c>
+      <c r="C5798" s="2">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="5799" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5799" s="1">
+        <v>45969</v>
+      </c>
+      <c r="C5799" s="2">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="5800" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5800" s="1">
+        <v>45970</v>
+      </c>
+      <c r="C5800" s="2">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="5801" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5801" s="1">
+        <v>45971</v>
+      </c>
+      <c r="C5801" s="2">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="5802" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5802" s="1">
+        <v>45972</v>
+      </c>
+      <c r="C5802" s="2">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="5803" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5803" s="1">
+        <v>45973</v>
+      </c>
+      <c r="C5803" s="2">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="5804" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5804" s="1">
+        <v>45974</v>
+      </c>
+      <c r="C5804" s="2">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="5805" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5805" s="1">
+        <v>45975</v>
+      </c>
+      <c r="C5805" s="2">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="5806" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5806" s="1">
+        <v>45976</v>
+      </c>
+      <c r="C5806" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="5807" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5807" s="1">
+        <v>45977</v>
+      </c>
+      <c r="C5807" s="2">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="5808" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5808" s="1">
+        <v>45978</v>
+      </c>
+      <c r="C5808" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5809" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5809" s="1">
+        <v>45979</v>
+      </c>
+      <c r="C5809" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="5810" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5810" s="1">
+        <v>45980</v>
+      </c>
+      <c r="C5810" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5811" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5811" s="1">
+        <v>45981</v>
+      </c>
+      <c r="C5811" s="2">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="5812" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5812" s="1">
+        <v>45982</v>
+      </c>
+      <c r="C5812" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="5813" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5813" s="1">
+        <v>45983</v>
+      </c>
+      <c r="C5813" s="2">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="5814" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5814" s="1">
+        <v>45984</v>
+      </c>
+      <c r="C5814" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5815" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5815" s="1">
+        <v>45985</v>
+      </c>
+      <c r="C5815" s="2">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="5816" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5816" s="1">
+        <v>45986</v>
+      </c>
+      <c r="C5816" s="2">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="5817" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5817" s="1">
+        <v>45987</v>
+      </c>
+      <c r="C5817" s="2">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="5818" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5818" s="1">
+        <v>45988</v>
+      </c>
+      <c r="C5818" s="2">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="5819" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5819" s="1">
+        <v>45989</v>
+      </c>
+      <c r="C5819" s="2">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="5820" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5820" s="1">
+        <v>45990</v>
+      </c>
+      <c r="C5820" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5821" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5821" s="1">
+        <v>45991</v>
+      </c>
+      <c r="C5821" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="5822" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5822" s="1">
+        <v>45992</v>
+      </c>
+      <c r="C5822" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="5823" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5823" s="1">
+        <v>45993</v>
+      </c>
+      <c r="C5823" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5824" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5824" s="1">
+        <v>45994</v>
+      </c>
+      <c r="C5824" s="2">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="5825" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5825" s="1">
+        <v>45995</v>
+      </c>
+      <c r="C5825" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5826" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5826" s="1">
+        <v>45996</v>
+      </c>
+      <c r="C5826" s="2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5827" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5827" s="1">
+        <v>45997</v>
+      </c>
+      <c r="C5827" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="5828" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5828" s="1">
+        <v>45998</v>
+      </c>
+      <c r="C5828" s="2">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="5829" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5829" s="1">
+        <v>45999</v>
+      </c>
+      <c r="C5829" s="2">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="5830" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5830" s="1">
+        <v>46000</v>
+      </c>
+      <c r="C5830" s="2">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="5831" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5831" s="1">
+        <v>46001</v>
+      </c>
+      <c r="C5831" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="5832" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5832" s="1">
+        <v>46002</v>
+      </c>
+      <c r="C5832" s="2">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="5833" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5833" s="1">
+        <v>46003</v>
+      </c>
+      <c r="C5833" s="2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5834" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5834" s="1">
+        <v>46004</v>
+      </c>
+      <c r="C5834" s="2">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5835" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5835" s="1">
+        <v>46005</v>
+      </c>
+      <c r="C5835" s="2">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="5836" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5836" s="1">
+        <v>46006</v>
+      </c>
+      <c r="C5836" s="2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5837" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5837" s="1">
+        <v>46007</v>
+      </c>
+      <c r="C5837" s="2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="5838" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5838" s="1">
+        <v>46008</v>
+      </c>
+      <c r="C5838" s="2">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="5839" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5839" s="1">
+        <v>46009</v>
+      </c>
+      <c r="C5839" s="2">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="5840" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5840" s="1">
+        <v>46010</v>
+      </c>
+      <c r="C5840" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="5841" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5841" s="1">
+        <v>46011</v>
+      </c>
+      <c r="C5841" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="5842" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5842" s="1">
+        <v>46012</v>
+      </c>
+      <c r="C5842" s="2">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="5843" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5843" s="1">
+        <v>46013</v>
+      </c>
+      <c r="C5843" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="5844" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5844" s="1">
+        <v>46014</v>
+      </c>
+      <c r="C5844" s="2">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="5845" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5845" s="1">
+        <v>46015</v>
+      </c>
+      <c r="C5845" s="2">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="5846" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5846" s="1">
+        <v>46016</v>
+      </c>
+      <c r="C5846" s="2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="5847" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5847" s="1">
+        <v>46017</v>
+      </c>
+      <c r="C5847" s="2">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="5848" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5848" s="1">
+        <v>46018</v>
+      </c>
+      <c r="C5848" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="5849" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5849" s="1">
+        <v>46019</v>
+      </c>
+      <c r="C5849" s="2">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="5850" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5850" s="1">
+        <v>46020</v>
+      </c>
+      <c r="C5850" s="2">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="5851" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5851" s="1">
+        <v>46021</v>
+      </c>
+      <c r="C5851" s="2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="5852" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5852" s="1">
+        <v>46022</v>
+      </c>
+      <c r="C5852" s="2">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="5853" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5853" s="1">
+        <v>46023</v>
+      </c>
+      <c r="C5853" s="2">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="5854" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5854" s="1">
+        <v>46024</v>
+      </c>
+      <c r="C5854" s="2">
+        <v>-4.3</v>
+      </c>
+    </row>
+    <row r="5855" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5855" s="1">
+        <v>46025</v>
+      </c>
+      <c r="C5855" s="2">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="5856" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5856" s="1">
+        <v>46026</v>
+      </c>
+      <c r="C5856" s="2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="5857" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5857" s="1">
+        <v>46027</v>
+      </c>
+      <c r="C5857" s="2">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="5858" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5858" s="1">
+        <v>46028</v>
+      </c>
+      <c r="C5858" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="5859" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5859" s="1">
+        <v>46029</v>
+      </c>
+      <c r="C5859" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="5860" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5860" s="1">
+        <v>46030</v>
+      </c>
+      <c r="C5860" s="2">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="5861" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5861" s="1">
+        <v>46031</v>
+      </c>
+      <c r="C5861" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5862" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5862" s="1">
+        <v>46032</v>
+      </c>
+      <c r="C5862" s="2">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="5863" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5863" s="1">
+        <v>46033</v>
+      </c>
+      <c r="C5863" s="2">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="5864" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5864" s="1">
+        <v>46034</v>
+      </c>
+      <c r="C5864" s="2">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="5865" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5865" s="1">
+        <v>46035</v>
+      </c>
+      <c r="C5865" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="5866" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5866" s="1">
+        <v>46036</v>
+      </c>
+      <c r="C5866" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5867" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5867" s="1">
+        <v>46037</v>
+      </c>
+      <c r="C5867" s="2">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="5868" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5868" s="1">
+        <v>46038</v>
+      </c>
+      <c r="C5868" s="2">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="5869" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5869" s="1">
+        <v>46039</v>
+      </c>
+      <c r="C5869" s="2">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5870" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5870" s="1">
+        <v>46040</v>
+      </c>
+      <c r="C5870" s="2">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="5871" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5871" s="1">
+        <v>46041</v>
+      </c>
+      <c r="C5871" s="2">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="5872" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5872" s="1">
+        <v>46042</v>
+      </c>
+      <c r="C5872" s="2">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="5873" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5873" s="1">
+        <v>46043</v>
+      </c>
+      <c r="C5873" s="2">
+        <v>-4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="5874" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5874" s="1">
+        <v>46044</v>
+      </c>
+      <c r="C5874" s="2">
+        <v>-5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="5875" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5875" s="1">
+        <v>46045</v>
+      </c>
+      <c r="C5875" s="2">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="5876" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5876" s="1">
+        <v>46046</v>
+      </c>
+      <c r="C5876" s="2">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="5877" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5877" s="1">
+        <v>46047</v>
+      </c>
+      <c r="C5877" s="2">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="5878" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5878" s="1">
+        <v>46048</v>
+      </c>
+      <c r="C5878" s="2">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="5879" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5879" s="1">
+        <v>46049</v>
+      </c>
+      <c r="C5879" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5880" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5880" s="1">
+        <v>46050</v>
+      </c>
+      <c r="C5880" s="2">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="5881" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5881" s="1">
+        <v>46051</v>
+      </c>
+      <c r="C5881" s="2">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="5882" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5882" s="1">
+        <v>46052</v>
+      </c>
+      <c r="C5882" s="2">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="5883" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5883" s="1">
+        <v>46053</v>
+      </c>
+      <c r="C5883" s="2">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="5884" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5884" s="1">
+        <v>46054</v>
+      </c>
+      <c r="C5884" s="2">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="5885" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5885" s="1">
+        <v>46055</v>
+      </c>
+      <c r="C5885" s="2">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="5886" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5886" s="1">
+        <v>46056</v>
+      </c>
+      <c r="C5886" s="2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5887" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5887" s="1">
+        <v>46057</v>
+      </c>
+      <c r="C5887" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5888" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5888" s="1">
+        <v>46058</v>
+      </c>
+      <c r="C5888" s="2">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="5889" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5889" s="1">
+        <v>46059</v>
+      </c>
+      <c r="C5889" s="2">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="5890" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5890" s="1">
+        <v>46060</v>
+      </c>
+      <c r="C5890" s="2">
+        <v>-2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="5891" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5891" s="1">
+        <v>46061</v>
+      </c>
+      <c r="C5891" s="2">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="5892" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5892" s="1">
+        <v>46062</v>
+      </c>
+      <c r="C5892" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5893" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5893" s="1">
+        <v>46063</v>
+      </c>
+      <c r="C5893" s="2">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="5894" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5894" s="1">
+        <v>46064</v>
+      </c>
+      <c r="C5894" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="5895" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5895" s="1">
+        <v>46065</v>
+      </c>
+      <c r="C5895" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="5896" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5896" s="1">
+        <v>46066</v>
+      </c>
+      <c r="C5896" s="2">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="5897" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5897" s="1">
+        <v>46067</v>
+      </c>
+      <c r="C5897" s="2">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="5898" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5898" s="1">
+        <v>46068</v>
+      </c>
+      <c r="C5898" s="2">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="5899" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5899" s="1">
+        <v>46069</v>
+      </c>
+      <c r="C5899" s="2">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="5900" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5900" s="1">
+        <v>46070</v>
+      </c>
+      <c r="C5900" s="2">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="5901" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5901" s="1">
+        <v>46071</v>
+      </c>
+      <c r="C5901" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="5902" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5902" s="1">
+        <v>46072</v>
+      </c>
+      <c r="C5902" s="2">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="5903" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5903" s="1">
+        <v>46073</v>
+      </c>
+      <c r="C5903" s="2">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="5904" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5904" s="1">
+        <v>46074</v>
+      </c>
+      <c r="C5904" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="5905" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5905" s="1">
+        <v>46075</v>
+      </c>
+      <c r="C5905" s="2">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="5906" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5906" s="1">
+        <v>46076</v>
+      </c>
+      <c r="C5906" s="2">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="5907" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5907" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C5907" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="5908" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5908" s="1">
+        <v>46078</v>
+      </c>
+      <c r="C5908" s="2">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="5909" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5909" s="1">
+        <v>46079</v>
+      </c>
+      <c r="C5909" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="5910" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5910" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C5910" s="2">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="5911" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5911" s="1">
+        <v>46081</v>
+      </c>
+      <c r="C5911" s="2">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="5912" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5912" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C5912" s="2">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="5913" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5913" s="1">
+        <v>46083</v>
+      </c>
+      <c r="C5913" s="2">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="5914" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5914" s="1">
+        <v>46084</v>
+      </c>
+      <c r="C5914" s="2">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="5915" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5915" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C5915" s="2">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="5916" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5916" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C5916" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5917" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5917" s="1">
+        <v>46087</v>
+      </c>
+      <c r="C5917" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5918" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5918" s="1">
+        <v>46088</v>
+      </c>
+      <c r="C5918" s="2">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="5919" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5919" s="1">
+        <v>46089</v>
+      </c>
+      <c r="C5919" s="2">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="5920" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5920" s="1">
+        <v>46090</v>
+      </c>
+      <c r="C5920" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="5921" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5921" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C5921" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5922" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5922" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C5922" s="2">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="5923" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5923" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C5923" s="2">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="5924" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5924" s="1">
+        <v>46094</v>
+      </c>
+      <c r="C5924" s="2">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="5925" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5925" s="1">
+        <v>46095</v>
+      </c>
+      <c r="C5925" s="2">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="5926" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5926" s="1">
+        <v>46096</v>
+      </c>
+      <c r="C5926" s="2">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="5927" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5927" s="1">
+        <v>46097</v>
+      </c>
+      <c r="C5927" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5928" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5928" s="1">
+        <v>46098</v>
+      </c>
+      <c r="C5928" s="2">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="5929" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5929" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C5929" s="2">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="5930" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5930" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C5930" s="2">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="5931" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5931" s="1">
+        <v>46101</v>
+      </c>
+      <c r="C5931" s="2">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="5932" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5932" s="1">
+        <v>46102</v>
+      </c>
+      <c r="C5932" s="2">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="5933" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5933" s="1">
+        <v>46103</v>
+      </c>
+      <c r="C5933" s="2">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="5934" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5934" s="1">
+        <v>46104</v>
+      </c>
+      <c r="C5934" s="2">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="5935" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5935" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C5935" s="2">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="5936" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5936" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C5936" s="2">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="5937" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5937" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C5937" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5938" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5938" s="1">
+        <v>46108</v>
+      </c>
+      <c r="C5938" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5939" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5939" s="1">
+        <v>46109</v>
+      </c>
+      <c r="C5939" s="2">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="5940" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5940" s="1">
+        <v>46110</v>
+      </c>
+      <c r="C5940" s="2">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="5941" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5941" s="1">
+        <v>46111</v>
+      </c>
+      <c r="C5941" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5942" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5942" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C5942" s="2">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="5943" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5943" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="5944" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5944" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="5945" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5945" s="1">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="5946" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5946" s="1">
+        <v>46116</v>
+      </c>
+    </row>
+    <row r="5947" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5947" s="1">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="5948" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5948" s="1">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="5949" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5949" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="5950" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5950" s="1">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="5951" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5951" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="5952" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5952" s="1">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="5953" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5953" s="1">
+        <v>46123</v>
+      </c>
+    </row>
+    <row r="5954" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5954" s="1">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="5955" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5955" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="5956" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5956" s="1">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="5957" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5957" s="1">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="5958" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5958" s="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="5959" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5959" s="1">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="5960" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5960" s="1">
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="5961" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5961" s="1">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="5962" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5962" s="1">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="5963" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5963" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="5964" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5964" s="1">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="5965" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5965" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="5966" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5966" s="1">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="5967" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5967" s="1">
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="5968" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5968" s="1">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="5969" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5969" s="1">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="5970" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5970" s="1">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="5971" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5971" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="5972" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5972" s="1">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="5973" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5973" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="5974" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5974" s="1">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="5975" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5975" s="1">
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="5976" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5976" s="1">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="5977" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5977" s="1">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="5978" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5978" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="5979" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5979" s="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="5980" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5980" s="1">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="5981" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5981" s="1">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="5982" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5982" s="1">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="5983" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5983" s="1">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="5984" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5984" s="1">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="5985" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5985" s="1">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="5986" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5986" s="1">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="5987" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5987" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="5988" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5988" s="1">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="5989" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5989" s="1">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="5990" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5990" s="1">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="5991" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5991" s="1">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="5992" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5992" s="1">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="5993" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5993" s="1">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="5994" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5994" s="1">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="5995" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5995" s="1">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="5996" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5996" s="1">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="5997" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5997" s="1">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="5998" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5998" s="1">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="5999" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5999" s="1">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="6000" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6000" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="6001" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6001" s="1">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="6002" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6002" s="1">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="6003" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6003" s="1">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="6004" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6004" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="6005" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6005" s="1">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="6006" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6006" s="1">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="6007" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6007" s="1">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="6008" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6008" s="1">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="6009" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6009" s="1">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="6010" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6010" s="1">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="6011" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6011" s="1">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="6012" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6012" s="1">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="6013" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6013" s="1">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="6014" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6014" s="1">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="6015" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6015" s="1">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="6016" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6016" s="1">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="6017" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6017" s="1">
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="6018" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6018" s="1">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="6019" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6019" s="1">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="6020" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6020" s="1">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="6021" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6021" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="6022" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6022" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="6023" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6023" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="6024" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6024" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="6025" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6025" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="6026" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6026" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="6027" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6027" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="6028" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6028" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="6029" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6029" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="6030" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6030" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="6031" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6031" s="1">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="6032" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6032" s="1">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="6033" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6033" s="1">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="6034" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6034" s="1">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="6035" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6035" s="1">
+        <v>46205</v>
+      </c>
+    </row>
+    <row r="6036" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6036" s="1">
+        <v>46206</v>
+      </c>
+    </row>
+    <row r="6037" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6037" s="1">
+        <v>46207</v>
+      </c>
+    </row>
+    <row r="6038" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6038" s="1">
+        <v>46208</v>
+      </c>
+    </row>
+    <row r="6039" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6039" s="1">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="6040" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6040" s="1">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="6041" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6041" s="1">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="6042" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6042" s="1">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="6043" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6043" s="1">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="6044" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6044" s="1">
+        <v>46214</v>
+      </c>
+    </row>
+    <row r="6045" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6045" s="1">
+        <v>46215</v>
+      </c>
+    </row>
+    <row r="6046" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6046" s="1">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="6047" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6047" s="1">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="6048" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6048" s="1">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="6049" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6049" s="1">
+        <v>46219</v>
+      </c>
+    </row>
+    <row r="6050" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6050" s="1">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="6051" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6051" s="1">
+        <v>46221</v>
+      </c>
+    </row>
+    <row r="6052" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6052" s="1">
+        <v>46222</v>
+      </c>
+    </row>
+    <row r="6053" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6053" s="1">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="6054" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6054" s="1">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="6055" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6055" s="1">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="6056" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6056" s="1">
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="6057" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6057" s="1">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="6058" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6058" s="1">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="6059" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6059" s="1">
+        <v>46229</v>
+      </c>
+    </row>
+    <row r="6060" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6060" s="1">
+        <v>46230</v>
+      </c>
+    </row>
+    <row r="6061" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6061" s="1">
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="6062" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6062" s="1">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="6063" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6063" s="1">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="6064" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6064" s="1">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="6065" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6065" s="1">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="6066" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6066" s="1">
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="6067" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6067" s="1">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="6068" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6068" s="1">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="6069" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6069" s="1">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="6070" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6070" s="1">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="6071" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6071" s="1">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="6072" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6072" s="1">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="6073" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6073" s="1">
+        <v>46243</v>
+      </c>
+    </row>
+    <row r="6074" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6074" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="6075" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6075" s="1">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="6076" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6076" s="1">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="6077" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6077" s="1">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="6078" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6078" s="1">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="6079" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6079" s="1">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="6080" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6080" s="1">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="6081" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6081" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="6082" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6082" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="6083" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6083" s="1">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="6084" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6084" s="1">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="6085" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6085" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="6086" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6086" s="1">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="6087" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6087" s="1">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="6088" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6088" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="6089" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6089" s="1">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="6090" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6090" s="1">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="6091" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6091" s="1">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="6092" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6092" s="1">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="6093" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6093" s="1">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="6094" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6094" s="1">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="6095" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6095" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="6096" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6096" s="1">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="6097" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6097" s="1">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="6098" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6098" s="1">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="6099" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6099" s="1">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="6100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6100" s="1">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="6101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6101" s="1">
+        <v>46271</v>
+      </c>
+    </row>
+    <row r="6102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6102" s="1">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="6103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6103" s="1">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="6104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6104" s="1">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="6105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6105" s="1">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="6106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6106" s="1">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="6107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6107" s="1">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="6108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6108" s="1">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="6109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6109" s="1">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="6110" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6110" s="1">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="6111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6111" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="6112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6112" s="1">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="6113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6113" s="1">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="6114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6114" s="1">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="6115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6115" s="1">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="6116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6116" s="1">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="6117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6117" s="1">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="6118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6118" s="1">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="6119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6119" s="1">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="6120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6120" s="1">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="6121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6121" s="1">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="6122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6122" s="1">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="6123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6123" s="1">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="6124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6124" s="1">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="6125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6125" s="1">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="6126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6126" s="1">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="6127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6127" s="1">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="6128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6128" s="1">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="6129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6129" s="1">
+        <v>46299</v>
+      </c>
+    </row>
+    <row r="6130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6130" s="1">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="6131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6131" s="1">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="6132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6132" s="1">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="6133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6133" s="1">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="6134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6134" s="1">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="6135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6135" s="1">
+        <v>46305</v>
+      </c>
+    </row>
+    <row r="6136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6136" s="1">
+        <v>46306</v>
+      </c>
+    </row>
+    <row r="6137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6137" s="1">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="6138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6138" s="1">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="6139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6139" s="1">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="6140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6140" s="1">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="6141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6141" s="1">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="6142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6142" s="1">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="6143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6143" s="1">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="6144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6144" s="1">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="6145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6145" s="1">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="6146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6146" s="1">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="6147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6147" s="1">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="6148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6148" s="1">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="6149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6149" s="1">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="6150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6150" s="1">
+        <v>46320</v>
+      </c>
+    </row>
+    <row r="6151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6151" s="1">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="6152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6152" s="1">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="6153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6153" s="1">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="6154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6154" s="1">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="6155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6155" s="1">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="6156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6156" s="1">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="6157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6157" s="1">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="6158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6158" s="1">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="6159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6159" s="1">
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="6160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6160" s="1">
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="6161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6161" s="1">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="6162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6162" s="1">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="6163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6163" s="1">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="6164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6164" s="1">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="6165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6165" s="1">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="6166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6166" s="1">
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="6167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6167" s="1">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="6168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6168" s="1">
+        <v>46338</v>
+      </c>
+    </row>
+    <row r="6169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6169" s="1">
+        <v>46339</v>
+      </c>
+    </row>
+    <row r="6170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6170" s="1">
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="6171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6171" s="1">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="6172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6172" s="1">
+        <v>46342</v>
+      </c>
+    </row>
+    <row r="6173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6173" s="1">
+        <v>46343</v>
+      </c>
+    </row>
+    <row r="6174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6174" s="1">
+        <v>46344</v>
+      </c>
+    </row>
+    <row r="6175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6175" s="1">
+        <v>46345</v>
+      </c>
+    </row>
+    <row r="6176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6176" s="1">
+        <v>46346</v>
+      </c>
+    </row>
+    <row r="6177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6177" s="1">
+        <v>46347</v>
+      </c>
+    </row>
+    <row r="6178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6178" s="1">
+        <v>46348</v>
+      </c>
+    </row>
+    <row r="6179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6179" s="1">
+        <v>46349</v>
+      </c>
+    </row>
+    <row r="6180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6180" s="1">
+        <v>46350</v>
+      </c>
+    </row>
+    <row r="6181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6181" s="1">
+        <v>46351</v>
+      </c>
+    </row>
+    <row r="6182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6182" s="1">
+        <v>46352</v>
+      </c>
+    </row>
+    <row r="6183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6183" s="1">
+        <v>46353</v>
+      </c>
+    </row>
+    <row r="6184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6184" s="1">
+        <v>46354</v>
+      </c>
+    </row>
+    <row r="6185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6185" s="1">
+        <v>46355</v>
+      </c>
+    </row>
+    <row r="6186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6186" s="1">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="6187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6187" s="1">
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="6188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6188" s="1">
+        <v>46358</v>
+      </c>
+    </row>
+    <row r="6189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6189" s="1">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="6190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6190" s="1">
+        <v>46360</v>
+      </c>
+    </row>
+    <row r="6191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6191" s="1">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="6192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6192" s="1">
+        <v>46362</v>
+      </c>
+    </row>
+    <row r="6193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6193" s="1">
+        <v>46363</v>
+      </c>
+    </row>
+    <row r="6194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6194" s="1">
+        <v>46364</v>
+      </c>
+    </row>
+    <row r="6195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6195" s="1">
+        <v>46365</v>
+      </c>
+    </row>
+    <row r="6196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6196" s="1">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="6197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6197" s="1">
+        <v>46367</v>
+      </c>
+    </row>
+    <row r="6198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6198" s="1">
+        <v>46368</v>
+      </c>
+    </row>
+    <row r="6199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6199" s="1">
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="6200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6200" s="1">
+        <v>46370</v>
+      </c>
+    </row>
+    <row r="6201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6201" s="1">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="6202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6202" s="1">
+        <v>46372</v>
+      </c>
+    </row>
+    <row r="6203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6203" s="1">
+        <v>46373</v>
+      </c>
+    </row>
+    <row r="6204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6204" s="1">
+        <v>46374</v>
+      </c>
+    </row>
+    <row r="6205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6205" s="1">
+        <v>46375</v>
+      </c>
+    </row>
+    <row r="6206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6206" s="1">
+        <v>46376</v>
+      </c>
+    </row>
+    <row r="6207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6207" s="1">
+        <v>46377</v>
+      </c>
+    </row>
+    <row r="6208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6208" s="1">
+        <v>46378</v>
+      </c>
+    </row>
+    <row r="6209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6209" s="1">
+        <v>46379</v>
+      </c>
+    </row>
+    <row r="6210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6210" s="1">
+        <v>46380</v>
+      </c>
+    </row>
+    <row r="6211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6211" s="1">
+        <v>46381</v>
+      </c>
+    </row>
+    <row r="6212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6212" s="1">
+        <v>46382</v>
+      </c>
+    </row>
+    <row r="6213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6213" s="1">
+        <v>46383</v>
+      </c>
+    </row>
+    <row r="6214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6214" s="1">
+        <v>46384</v>
+      </c>
+    </row>
+    <row r="6215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6215" s="1">
+        <v>46385</v>
+      </c>
+    </row>
+    <row r="6216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6216" s="1">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="6217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6217" s="1">
+        <v>46387</v>
       </c>
     </row>
   </sheetData>
